--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9100,0.0088,0.0241,0.0227</t>
-  </si>
-  <si>
-    <t>0.0229,0.0030,0.0056,0.9861</t>
-  </si>
-  <si>
-    <t>0.7027,0.0065,0.0249,0.2423</t>
-  </si>
-  <si>
-    <t>0.0422,0.0080,0.0151,0.9689</t>
-  </si>
-  <si>
-    <t>0.9852,0.0089,0.0024,0.0010</t>
-  </si>
-  <si>
-    <t>0.9922,0.0036,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9926,0.0027,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9904,0.0005,0.0014,0.0030</t>
-  </si>
-  <si>
-    <t>0.9935,0.0016,0.0001,0.0014</t>
-  </si>
-  <si>
-    <t>0.9858,0.0121,0.0014,0.0010</t>
-  </si>
-  <si>
-    <t>0.9835,0.0050,0.0027,0.0033</t>
-  </si>
-  <si>
-    <t>0.9946,0.0011,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.7399,0.0370,0.2371,0.0026</t>
-  </si>
-  <si>
-    <t>0.3860,0.0347,0.6943,0.0021</t>
-  </si>
-  <si>
-    <t>0.6254,0.0152,0.5202,0.0015</t>
-  </si>
-  <si>
-    <t>0.1207,0.0505,0.8250,0.0103</t>
-  </si>
-  <si>
-    <t>0.8800,0.0046,0.1255,0.0032</t>
-  </si>
-  <si>
-    <t>0.0093,0.9760,0.0403,0.0013</t>
-  </si>
-  <si>
-    <t>0.0053,0.9916,0.0048,0.0002</t>
-  </si>
-  <si>
-    <t>0.1208,0.8592,0.0232,0.0036</t>
-  </si>
-  <si>
-    <t>0.0605,0.9200,0.0153,0.0051</t>
-  </si>
-  <si>
-    <t>0.0054,0.9872,0.0036,0.0009</t>
-  </si>
-  <si>
-    <t>0.3498,0.0349,0.4396,0.1542</t>
-  </si>
-  <si>
-    <t>0.3430,0.0104,0.7219,0.0125</t>
-  </si>
-  <si>
-    <t>0.0118,0.0309,0.9790,0.0007</t>
-  </si>
-  <si>
-    <t>0.1205,0.0605,0.8063,0.0485</t>
-  </si>
-  <si>
-    <t>0.2599,0.0465,0.7805,0.0094</t>
-  </si>
-  <si>
-    <t>0.0584,0.0022,0.9738,0.0016</t>
-  </si>
-  <si>
-    <t>0.0084,0.0110,0.9741,0.0114</t>
-  </si>
-  <si>
-    <t>0.5613,0.4461,0.0427,0.0112</t>
-  </si>
-  <si>
-    <t>0.4614,0.1356,0.4540,0.0024</t>
-  </si>
-  <si>
-    <t>0.0158,0.0397,0.9792,0.0038</t>
-  </si>
-  <si>
-    <t>0.0125,0.9315,0.1823,0.0006</t>
-  </si>
-  <si>
-    <t>0.7758,0.0513,0.0184,0.0695</t>
-  </si>
-  <si>
-    <t>0.1481,0.1432,0.7850,0.0143</t>
-  </si>
-  <si>
-    <t>0.7141,0.3285,0.0261,0.0025</t>
-  </si>
-  <si>
-    <t>0.0426,0.9106,0.1624,0.0015</t>
-  </si>
-  <si>
-    <t>0.0143,0.8411,0.4958,0.0014</t>
-  </si>
-  <si>
-    <t>0.0180,0.1401,0.9477,0.0116</t>
-  </si>
-  <si>
-    <t>0.0759,0.0454,0.9325,0.0059</t>
-  </si>
-  <si>
-    <t>0.0285,0.0025,0.6143,0.4659</t>
-  </si>
-  <si>
-    <t>0.0453,0.1737,0.8961,0.0027</t>
-  </si>
-  <si>
-    <t>0.0119,0.9631,0.0404,0.0011</t>
-  </si>
-  <si>
-    <t>0.0227,0.0302,0.9618,0.0033</t>
-  </si>
-  <si>
-    <t>0.0358,0.6988,0.0039,0.7895</t>
-  </si>
-  <si>
-    <t>0.0017,0.9900,0.0087,0.0033</t>
-  </si>
-  <si>
-    <t>0.0055,0.9668,0.0516,0.0081</t>
-  </si>
-  <si>
-    <t>0.0021,0.9761,0.0251,0.0249</t>
-  </si>
-  <si>
-    <t>0.0131,0.3830,0.9224,0.0051</t>
-  </si>
-  <si>
-    <t>0.0070,0.1808,0.9871,0.0005</t>
-  </si>
-  <si>
-    <t>0.1098,0.0201,0.8722,0.0159</t>
-  </si>
-  <si>
-    <t>0.0102,0.0017,0.9888,0.0028</t>
-  </si>
-  <si>
-    <t>0.0010,0.0041,0.9945,0.0056</t>
-  </si>
-  <si>
-    <t>0.0152,0.1003,0.9446,0.0020</t>
-  </si>
-  <si>
-    <t>0.8947,0.1580,0.0035,0.0027</t>
-  </si>
-  <si>
-    <t>0.9261,0.0259,0.0506,0.0052</t>
-  </si>
-  <si>
-    <t>0.9819,0.0155,0.0023,0.0008</t>
-  </si>
-  <si>
-    <t>0.0165,0.0347,0.9795,0.0060</t>
-  </si>
-  <si>
-    <t>0.9841,0.0045,0.0024,0.0030</t>
-  </si>
-  <si>
-    <t>0.9404,0.0595,0.0053,0.0027</t>
-  </si>
-  <si>
-    <t>0.9055,0.0770,0.0240,0.0042</t>
-  </si>
-  <si>
-    <t>0.0014,0.7523,0.9747,0.0002</t>
-  </si>
-  <si>
-    <t>0.0175,0.0213,0.9854,0.0005</t>
-  </si>
-  <si>
-    <t>0.0019,0.0057,0.9919,0.0048</t>
-  </si>
-  <si>
-    <t>0.0063,0.8319,0.8926,0.0019</t>
-  </si>
-  <si>
-    <t>0.0042,0.0046,0.9944,0.0009</t>
-  </si>
-  <si>
-    <t>0.0117,0.9304,0.2034,0.0007</t>
-  </si>
-  <si>
-    <t>0.0129,0.9882,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9723,0.0047,0.0116,0.0011</t>
-  </si>
-  <si>
-    <t>0.8295,0.0309,0.1250,0.0193</t>
-  </si>
-  <si>
-    <t>0.0844,0.0759,0.9042,0.0132</t>
-  </si>
-  <si>
-    <t>0.0001,0.9851,0.7811,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9691,0.7154,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.9579,0.4373,0.0004</t>
-  </si>
-  <si>
-    <t>0.0019,0.9643,0.6728,0.0002</t>
-  </si>
-  <si>
-    <t>0.0297,0.0025,0.0147,0.9754</t>
-  </si>
-  <si>
-    <t>0.0021,0.0157,0.0002,0.9985</t>
-  </si>
-  <si>
-    <t>0.0028,0.0007,0.0026,0.9956</t>
-  </si>
-  <si>
-    <t>0.0283,0.0101,0.0039,0.9827</t>
-  </si>
-  <si>
-    <t>0.0378,0.0031,0.0138,0.9699</t>
-  </si>
-  <si>
-    <t>0.0045,0.0054,0.0231,0.9866</t>
-  </si>
-  <si>
-    <t>0.0017,0.9514,0.5843,0.0001</t>
-  </si>
-  <si>
-    <t>0.0062,0.6148,0.9433,0.0007</t>
-  </si>
-  <si>
-    <t>0.0268,0.4846,0.7900,0.0009</t>
-  </si>
-  <si>
-    <t>0.0033,0.8995,0.6732,0.0012</t>
-  </si>
-  <si>
-    <t>0.0022,0.8328,0.9028,0.0002</t>
-  </si>
-  <si>
-    <t>0.0235,0.6485,0.7147,0.0010</t>
-  </si>
-  <si>
-    <t>0.9916,0.0039,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9849,0.0043,0.0012,0.0030</t>
-  </si>
-  <si>
-    <t>0.8933,0.1125,0.0213,0.0023</t>
-  </si>
-  <si>
-    <t>0.9909,0.0028,0.0008,0.0014</t>
-  </si>
-  <si>
-    <t>0.9522,0.0340,0.0085,0.0055</t>
-  </si>
-  <si>
-    <t>0.9871,0.0054,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.9369,0.0541,0.0096,0.0093</t>
-  </si>
-  <si>
-    <t>0.9546,0.0302,0.0112,0.0043</t>
-  </si>
-  <si>
-    <t>0.9716,0.0140,0.0016,0.0040</t>
-  </si>
-  <si>
-    <t>0.9943,0.0014,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9829,0.0086,0.0009,0.0014</t>
-  </si>
-  <si>
-    <t>0.9928,0.0018,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9825,0.0016,0.0002,0.0075</t>
-  </si>
-  <si>
-    <t>0.9929,0.0038,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9944,0.0006,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9926,0.0007,0.0002,0.0022</t>
-  </si>
-  <si>
-    <t>0.0027,0.0009,0.9904,0.0098</t>
-  </si>
-  <si>
-    <t>0.0373,0.0106,0.9716,0.0009</t>
-  </si>
-  <si>
-    <t>0.3641,0.0702,0.1931,0.4504</t>
-  </si>
-  <si>
-    <t>0.0828,0.0139,0.9018,0.0077</t>
-  </si>
-  <si>
-    <t>0.1353,0.8943,0.0043,0.0011</t>
-  </si>
-  <si>
-    <t>0.0234,0.9672,0.0104,0.0027</t>
-  </si>
-  <si>
-    <t>0.0476,0.9370,0.0036,0.0088</t>
-  </si>
-  <si>
-    <t>0.2300,0.7939,0.0202,0.0039</t>
-  </si>
-  <si>
-    <t>0.0252,0.9649,0.0089,0.0003</t>
-  </si>
-  <si>
-    <t>0.0058,0.9887,0.0005,0.0027</t>
-  </si>
-  <si>
-    <t>0.1430,0.8570,0.0030,0.0078</t>
-  </si>
-  <si>
-    <t>0.6780,0.0637,0.1930,0.0559</t>
-  </si>
-  <si>
-    <t>0.2869,0.0296,0.7533,0.0070</t>
-  </si>
-  <si>
-    <t>0.6226,0.0726,0.0913,0.0611</t>
-  </si>
-  <si>
-    <t>0.6555,0.1339,0.1661,0.0028</t>
-  </si>
-  <si>
-    <t>0.2236,0.0235,0.1909,0.6915</t>
-  </si>
-  <si>
-    <t>0.0007,0.9913,0.0053,0.0066</t>
-  </si>
-  <si>
-    <t>0.0053,0.9735,0.0322,0.0092</t>
-  </si>
-  <si>
-    <t>0.0044,0.9605,0.0085,0.3407</t>
-  </si>
-  <si>
-    <t>0.0029,0.9539,0.6927,0.0004</t>
-  </si>
-  <si>
-    <t>0.0098,0.9712,0.1072,0.0008</t>
-  </si>
-  <si>
-    <t>0.8197,0.1667,0.0375,0.0048</t>
-  </si>
-  <si>
-    <t>0.6144,0.4410,0.0291,0.0012</t>
-  </si>
-  <si>
-    <t>0.8810,0.0757,0.0557,0.0040</t>
-  </si>
-  <si>
-    <t>0.9887,0.0022,0.0013,0.0021</t>
-  </si>
-  <si>
-    <t>0.9784,0.0011,0.0006,0.0144</t>
-  </si>
-  <si>
-    <t>0.9226,0.0527,0.0232,0.0049</t>
-  </si>
-  <si>
-    <t>0.9854,0.0046,0.0022,0.0017</t>
-  </si>
-  <si>
-    <t>0.9562,0.0132,0.0246,0.0025</t>
-  </si>
-  <si>
-    <t>0.9807,0.0099,0.0024,0.0019</t>
-  </si>
-  <si>
-    <t>0.9691,0.0036,0.0089,0.0086</t>
-  </si>
-  <si>
-    <t>0.0087,0.4608,0.9461,0.0023</t>
-  </si>
-  <si>
-    <t>0.0072,0.4611,0.8898,0.0002</t>
-  </si>
-  <si>
-    <t>0.0290,0.0767,0.9296,0.0095</t>
-  </si>
-  <si>
-    <t>0.0120,0.0888,0.9644,0.0017</t>
-  </si>
-  <si>
-    <t>0.6612,0.0498,0.3156,0.0251</t>
-  </si>
-  <si>
-    <t>0.4512,0.0779,0.5182,0.0227</t>
-  </si>
-  <si>
-    <t>0.6754,0.0035,0.4610,0.0096</t>
-  </si>
-  <si>
-    <t>0.4826,0.2279,0.3175,0.0283</t>
-  </si>
-  <si>
-    <t>0.0223,0.0035,0.0106,0.9812</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.0009,0.9990</t>
-  </si>
-  <si>
-    <t>0.0096,0.0040,0.0087,0.9882</t>
-  </si>
-  <si>
-    <t>0.0407,0.0018,0.0029,0.9817</t>
-  </si>
-  <si>
-    <t>0.0029,0.7491,0.8610,0.0029</t>
-  </si>
-  <si>
-    <t>0.9234,0.0869,0.0050,0.0056</t>
-  </si>
-  <si>
-    <t>0.3506,0.7091,0.0140,0.0130</t>
-  </si>
-  <si>
-    <t>0.9667,0.0069,0.0046,0.0091</t>
-  </si>
-  <si>
-    <t>0.9075,0.0728,0.0234,0.0035</t>
-  </si>
-  <si>
-    <t>0.9620,0.0022,0.0142,0.0088</t>
-  </si>
-  <si>
-    <t>0.2004,0.0024,0.0167,0.8773</t>
-  </si>
-  <si>
-    <t>0.9099,0.0141,0.0028,0.0492</t>
-  </si>
-  <si>
-    <t>0.0020,0.0227,0.9267,0.1476</t>
-  </si>
-  <si>
-    <t>0.7224,0.0009,0.0285,0.1848</t>
-  </si>
-  <si>
-    <t>0.8830,0.0035,0.0317,0.0422</t>
-  </si>
-  <si>
-    <t>0.5061,0.4246,0.0737,0.0243</t>
-  </si>
-  <si>
-    <t>0.8631,0.1174,0.0258,0.0056</t>
-  </si>
-  <si>
-    <t>0.5449,0.4073,0.0666,0.0726</t>
-  </si>
-  <si>
-    <t>0.0834,0.8688,0.0176,0.0261</t>
-  </si>
-  <si>
-    <t>0.7504,0.1413,0.1118,0.0041</t>
-  </si>
-  <si>
-    <t>0.8206,0.1074,0.0280,0.0402</t>
-  </si>
-  <si>
-    <t>0.9799,0.0047,0.0047,0.0040</t>
-  </si>
-  <si>
-    <t>0.9845,0.0069,0.0031,0.0013</t>
-  </si>
-  <si>
-    <t>0.9897,0.0030,0.0038,0.0006</t>
-  </si>
-  <si>
-    <t>0.9857,0.0041,0.0021,0.0022</t>
-  </si>
-  <si>
-    <t>0.9811,0.0012,0.0034,0.0047</t>
-  </si>
-  <si>
-    <t>0.9636,0.0277,0.0074,0.0017</t>
-  </si>
-  <si>
-    <t>0.9733,0.0145,0.0067,0.0018</t>
-  </si>
-  <si>
-    <t>0.9863,0.0028,0.0021,0.0034</t>
-  </si>
-  <si>
-    <t>0.3652,0.6369,0.0150,0.0105</t>
-  </si>
-  <si>
-    <t>0.6843,0.3996,0.0145,0.0056</t>
-  </si>
-  <si>
-    <t>0.3450,0.7010,0.0054,0.0141</t>
-  </si>
-  <si>
-    <t>0.7354,0.0946,0.2422,0.0230</t>
-  </si>
-  <si>
-    <t>0.7413,0.2622,0.0296,0.0094</t>
-  </si>
-  <si>
-    <t>0.9390,0.0531,0.0055,0.0043</t>
-  </si>
-  <si>
-    <t>0.9496,0.0413,0.0111,0.0024</t>
-  </si>
-  <si>
-    <t>0.8639,0.0915,0.0545,0.0038</t>
-  </si>
-  <si>
-    <t>0.0058,0.1070,0.9897,0.0008</t>
-  </si>
-  <si>
-    <t>0.8579,0.1247,0.0286,0.0082</t>
-  </si>
-  <si>
-    <t>0.0278,0.0142,0.9727,0.0005</t>
-  </si>
-  <si>
-    <t>0.0078,0.0341,0.9756,0.0098</t>
-  </si>
-  <si>
-    <t>0.0328,0.0193,0.9628,0.0044</t>
-  </si>
-  <si>
-    <t>0.0080,0.2590,0.9692,0.0020</t>
-  </si>
-  <si>
-    <t>0.1488,0.0136,0.9207,0.0012</t>
-  </si>
-  <si>
-    <t>0.0062,0.0040,0.9952,0.0003</t>
-  </si>
-  <si>
-    <t>0.0102,0.0052,0.9907,0.0002</t>
-  </si>
-  <si>
-    <t>0.4698,0.0644,0.4275,0.0813</t>
-  </si>
-  <si>
-    <t>0.0169,0.0626,0.9626,0.0022</t>
-  </si>
-  <si>
-    <t>0.1454,0.1216,0.7591,0.0153</t>
-  </si>
-  <si>
-    <t>0.4212,0.0708,0.5610,0.0019</t>
-  </si>
-  <si>
-    <t>0.2235,0.0213,0.7797,0.0205</t>
-  </si>
-  <si>
-    <t>0.3317,0.3656,0.3095,0.0123</t>
-  </si>
-  <si>
-    <t>0.4733,0.0185,0.6495,0.0074</t>
-  </si>
-  <si>
-    <t>0.3540,0.1366,0.5372,0.0273</t>
-  </si>
-  <si>
-    <t>0.7571,0.3012,0.0157,0.0027</t>
-  </si>
-  <si>
-    <t>0.5508,0.5358,0.0124,0.0030</t>
-  </si>
-  <si>
-    <t>0.6920,0.2540,0.0885,0.0278</t>
-  </si>
-  <si>
-    <t>0.9616,0.0215,0.0035,0.0068</t>
-  </si>
-  <si>
-    <t>0.9297,0.0644,0.0084,0.0057</t>
-  </si>
-  <si>
-    <t>0.5942,0.0395,0.3856,0.0426</t>
-  </si>
-  <si>
-    <t>0.9333,0.0105,0.0413,0.0016</t>
-  </si>
-  <si>
-    <t>0.7121,0.0082,0.2947,0.0206</t>
-  </si>
-  <si>
-    <t>0.8235,0.0073,0.2653,0.0036</t>
-  </si>
-  <si>
-    <t>0.8873,0.0043,0.1336,0.0019</t>
-  </si>
-  <si>
-    <t>0.2795,0.0684,0.7070,0.0192</t>
-  </si>
-  <si>
-    <t>0.0288,0.3414,0.8637,0.0072</t>
-  </si>
-  <si>
-    <t>0.0408,0.0324,0.9357,0.0296</t>
-  </si>
-  <si>
-    <t>0.0432,0.0272,0.9380,0.0144</t>
-  </si>
-  <si>
-    <t>0.0199,0.0855,0.9506,0.0015</t>
-  </si>
-  <si>
-    <t>0.9717,0.0095,0.0050,0.0038</t>
-  </si>
-  <si>
-    <t>0.9799,0.0045,0.0037,0.0043</t>
-  </si>
-  <si>
-    <t>0.9752,0.0070,0.0018,0.0058</t>
-  </si>
-  <si>
-    <t>0.9629,0.0332,0.0049,0.0018</t>
-  </si>
-  <si>
-    <t>0.9792,0.0097,0.0076,0.0012</t>
-  </si>
-  <si>
-    <t>0.9856,0.0085,0.0043,0.0007</t>
-  </si>
-  <si>
-    <t>0.9850,0.0044,0.0029,0.0024</t>
-  </si>
-  <si>
-    <t>0.9923,0.0016,0.0026,0.0005</t>
-  </si>
-  <si>
-    <t>0.1481,0.0420,0.8773,0.0161</t>
-  </si>
-  <si>
-    <t>0.2753,0.3713,0.3986,0.0186</t>
-  </si>
-  <si>
-    <t>0.7259,0.0801,0.0803,0.0793</t>
-  </si>
-  <si>
-    <t>0.0072,0.0133,0.9895,0.0005</t>
-  </si>
-  <si>
-    <t>0.0020,0.0060,0.9823,0.0237</t>
-  </si>
-  <si>
-    <t>0.0102,0.0277,0.9758,0.0025</t>
-  </si>
-  <si>
-    <t>0.0004,0.0019,0.9951,0.0099</t>
-  </si>
-  <si>
-    <t>0.1042,0.0147,0.9233,0.0044</t>
-  </si>
-  <si>
-    <t>0.0079,0.0045,0.9927,0.0006</t>
-  </si>
-  <si>
-    <t>0.0191,0.0423,0.9547,0.0032</t>
-  </si>
-  <si>
-    <t>0.0375,0.0532,0.9397,0.0028</t>
-  </si>
-  <si>
-    <t>0.8210,0.0052,0.2026,0.0107</t>
-  </si>
-  <si>
-    <t>0.6674,0.0159,0.3581,0.0299</t>
-  </si>
-  <si>
-    <t>0.8207,0.0079,0.2159,0.0034</t>
-  </si>
-  <si>
-    <t>0.8872,0.0981,0.0144,0.0079</t>
-  </si>
-  <si>
-    <t>0.9716,0.0216,0.0018,0.0020</t>
-  </si>
-  <si>
-    <t>0.9874,0.0060,0.0041,0.0006</t>
-  </si>
-  <si>
-    <t>0.9466,0.0524,0.0076,0.0020</t>
-  </si>
-  <si>
-    <t>0.9903,0.0026,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9913,0.0035,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9720,0.0188,0.0064,0.0012</t>
-  </si>
-  <si>
-    <t>0.9630,0.0331,0.0032,0.0021</t>
-  </si>
-  <si>
-    <t>0.0400,0.1572,0.8225,0.0297</t>
-  </si>
-  <si>
-    <t>0.0185,0.2106,0.9123,0.0059</t>
-  </si>
-  <si>
-    <t>0.0108,0.0573,0.9770,0.0037</t>
-  </si>
-  <si>
-    <t>0.1114,0.0459,0.8624,0.0008</t>
-  </si>
-  <si>
-    <t>0.0047,0.0172,0.9837,0.0107</t>
-  </si>
-  <si>
-    <t>0.2096,0.0092,0.7125,0.1054</t>
-  </si>
-  <si>
-    <t>0.0456,0.0155,0.9201,0.0265</t>
-  </si>
-  <si>
-    <t>0.0076,0.0149,0.8783,0.1649</t>
-  </si>
-  <si>
-    <t>0.9712,0.0017,0.0056,0.0070</t>
-  </si>
-  <si>
-    <t>0.0018,0.3028,0.0096,0.9873</t>
-  </si>
-  <si>
-    <t>0.0276,0.0119,0.0025,0.9859</t>
-  </si>
-  <si>
-    <t>0.0058,0.0017,0.0031,0.9941</t>
-  </si>
-  <si>
-    <t>0.0109,0.0012,0.0008,0.9943</t>
-  </si>
-  <si>
-    <t>0.8033,0.0597,0.0315,0.0911</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.0930,0.0372,0.0221,0.9351</t>
+  </si>
+  <si>
+    <t>0.0163,0.0022,0.0031,0.9901</t>
+  </si>
+  <si>
+    <t>0.6753,0.0036,0.0089,0.3704</t>
+  </si>
+  <si>
+    <t>0.0400,0.0090,0.0014,0.9848</t>
+  </si>
+  <si>
+    <t>0.9905,0.0058,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9966,0.0003,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9875,0.0037,0.0021,0.0009</t>
+  </si>
+  <si>
+    <t>0.9964,0.0003,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9483,0.0639,0.0030,0.0024</t>
+  </si>
+  <si>
+    <t>0.9730,0.0221,0.0020,0.0023</t>
+  </si>
+  <si>
+    <t>0.9881,0.0021,0.0009,0.0025</t>
+  </si>
+  <si>
+    <t>0.9888,0.0023,0.0015,0.0018</t>
+  </si>
+  <si>
+    <t>0.6516,0.0366,0.3597,0.0008</t>
+  </si>
+  <si>
+    <t>0.3120,0.2109,0.4807,0.0161</t>
+  </si>
+  <si>
+    <t>0.3444,0.0124,0.8071,0.0005</t>
+  </si>
+  <si>
+    <t>0.3004,0.1237,0.5501,0.0019</t>
+  </si>
+  <si>
+    <t>0.6060,0.0886,0.2839,0.0293</t>
+  </si>
+  <si>
+    <t>0.0105,0.9765,0.0198,0.0010</t>
+  </si>
+  <si>
+    <t>0.0036,0.9885,0.0113,0.0006</t>
+  </si>
+  <si>
+    <t>0.0204,0.9585,0.0030,0.0104</t>
+  </si>
+  <si>
+    <t>0.1215,0.8514,0.0669,0.0039</t>
+  </si>
+  <si>
+    <t>0.0021,0.9930,0.0163,0.0003</t>
+  </si>
+  <si>
+    <t>0.4718,0.0041,0.2679,0.1635</t>
+  </si>
+  <si>
+    <t>0.5103,0.0295,0.5555,0.0236</t>
+  </si>
+  <si>
+    <t>0.0369,0.0055,0.9704,0.0018</t>
+  </si>
+  <si>
+    <t>0.1030,0.0146,0.8745,0.0303</t>
+  </si>
+  <si>
+    <t>0.0312,0.0031,0.9719,0.0052</t>
+  </si>
+  <si>
+    <t>0.0556,0.0082,0.9279,0.0206</t>
+  </si>
+  <si>
+    <t>0.0056,0.0046,0.9862,0.0077</t>
+  </si>
+  <si>
+    <t>0.8352,0.1379,0.0296,0.0011</t>
+  </si>
+  <si>
+    <t>0.1647,0.0463,0.8691,0.0005</t>
+  </si>
+  <si>
+    <t>0.0119,0.0213,0.9772,0.0062</t>
+  </si>
+  <si>
+    <t>0.0065,0.9627,0.1235,0.0007</t>
+  </si>
+  <si>
+    <t>0.7750,0.0996,0.0537,0.0397</t>
+  </si>
+  <si>
+    <t>0.6931,0.0570,0.2605,0.0102</t>
+  </si>
+  <si>
+    <t>0.7213,0.3557,0.0142,0.0039</t>
+  </si>
+  <si>
+    <t>0.0431,0.9089,0.1685,0.0055</t>
+  </si>
+  <si>
+    <t>0.0429,0.3636,0.7296,0.0221</t>
+  </si>
+  <si>
+    <t>0.1320,0.0804,0.6785,0.1350</t>
+  </si>
+  <si>
+    <t>0.0224,0.1456,0.9410,0.0109</t>
+  </si>
+  <si>
+    <t>0.1114,0.0141,0.7843,0.1513</t>
+  </si>
+  <si>
+    <t>0.0247,0.0438,0.9648,0.0035</t>
+  </si>
+  <si>
+    <t>0.0063,0.9679,0.0507,0.0015</t>
+  </si>
+  <si>
+    <t>0.0174,0.0042,0.9747,0.0048</t>
+  </si>
+  <si>
+    <t>0.0149,0.8232,0.0179,0.9346</t>
+  </si>
+  <si>
+    <t>0.0016,0.9921,0.0076,0.0012</t>
+  </si>
+  <si>
+    <t>0.0113,0.9547,0.1205,0.0009</t>
+  </si>
+  <si>
+    <t>0.0025,0.9864,0.0445,0.0016</t>
+  </si>
+  <si>
+    <t>0.0092,0.8378,0.5395,0.0012</t>
+  </si>
+  <si>
+    <t>0.0158,0.5815,0.8951,0.0034</t>
+  </si>
+  <si>
+    <t>0.0424,0.0018,0.8989,0.0723</t>
+  </si>
+  <si>
+    <t>0.0865,0.0003,0.9495,0.0038</t>
+  </si>
+  <si>
+    <t>0.0020,0.0179,0.9847,0.0099</t>
+  </si>
+  <si>
+    <t>0.0352,0.2641,0.8536,0.0093</t>
+  </si>
+  <si>
+    <t>0.9665,0.0379,0.0024,0.0009</t>
+  </si>
+  <si>
+    <t>0.8815,0.0389,0.0853,0.0039</t>
+  </si>
+  <si>
+    <t>0.5979,0.4889,0.0121,0.0145</t>
+  </si>
+  <si>
+    <t>0.0199,0.0773,0.9650,0.0032</t>
+  </si>
+  <si>
+    <t>0.9488,0.0345,0.0109,0.0038</t>
+  </si>
+  <si>
+    <t>0.9435,0.0374,0.0164,0.0046</t>
+  </si>
+  <si>
+    <t>0.8698,0.1056,0.0207,0.0143</t>
+  </si>
+  <si>
+    <t>0.0019,0.8000,0.9254,0.0002</t>
+  </si>
+  <si>
+    <t>0.0032,0.4708,0.9629,0.0016</t>
+  </si>
+  <si>
+    <t>0.0025,0.0261,0.9668,0.0272</t>
+  </si>
+  <si>
+    <t>0.0014,0.9158,0.9154,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.0028,0.9968,0.0027</t>
+  </si>
+  <si>
+    <t>0.0180,0.8625,0.2862,0.0005</t>
+  </si>
+  <si>
+    <t>0.0093,0.9902,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9032,0.0201,0.0831,0.0036</t>
+  </si>
+  <si>
+    <t>0.2280,0.2384,0.7006,0.0085</t>
+  </si>
+  <si>
+    <t>0.0121,0.2675,0.9361,0.0011</t>
+  </si>
+  <si>
+    <t>0.0085,0.8724,0.6632,0.0006</t>
+  </si>
+  <si>
+    <t>0.0061,0.8224,0.7611,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.9905,0.0618,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.8441,0.9859,0.0001</t>
+  </si>
+  <si>
+    <t>0.0518,0.0377,0.1176,0.9032</t>
+  </si>
+  <si>
+    <t>0.0011,0.0124,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0041,0.0008,0.0001,0.9985</t>
+  </si>
+  <si>
+    <t>0.0157,0.0014,0.0071,0.9842</t>
+  </si>
+  <si>
+    <t>0.0135,0.0082,0.0062,0.9884</t>
+  </si>
+  <si>
+    <t>0.0043,0.0012,0.0004,0.9978</t>
+  </si>
+  <si>
+    <t>0.0016,0.8191,0.9564,0.0004</t>
+  </si>
+  <si>
+    <t>0.0043,0.6581,0.9510,0.0005</t>
+  </si>
+  <si>
+    <t>0.0150,0.8783,0.3519,0.0057</t>
+  </si>
+  <si>
+    <t>0.0115,0.4092,0.8900,0.0050</t>
+  </si>
+  <si>
+    <t>0.0007,0.9519,0.8325,0.0001</t>
+  </si>
+  <si>
+    <t>0.0124,0.7518,0.8050,0.0018</t>
+  </si>
+  <si>
+    <t>0.9801,0.0098,0.0069,0.0008</t>
+  </si>
+  <si>
+    <t>0.9533,0.0263,0.0050,0.0044</t>
+  </si>
+  <si>
+    <t>0.9792,0.0124,0.0020,0.0016</t>
+  </si>
+  <si>
+    <t>0.9843,0.0059,0.0010,0.0017</t>
+  </si>
+  <si>
+    <t>0.8928,0.1080,0.0143,0.0047</t>
+  </si>
+  <si>
+    <t>0.9872,0.0024,0.0003,0.0039</t>
+  </si>
+  <si>
+    <t>0.9842,0.0028,0.0005,0.0058</t>
+  </si>
+  <si>
+    <t>0.9807,0.0099,0.0018,0.0026</t>
+  </si>
+  <si>
+    <t>0.9934,0.0013,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9889,0.0046,0.0036,0.0005</t>
+  </si>
+  <si>
+    <t>0.9835,0.0084,0.0020,0.0013</t>
+  </si>
+  <si>
+    <t>0.9938,0.0006,0.0002,0.0020</t>
+  </si>
+  <si>
+    <t>0.9862,0.0056,0.0015,0.0018</t>
+  </si>
+  <si>
+    <t>0.9910,0.0015,0.0002,0.0031</t>
+  </si>
+  <si>
+    <t>0.9916,0.0020,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9762,0.0126,0.0011,0.0029</t>
+  </si>
+  <si>
+    <t>0.0024,0.0091,0.9731,0.0581</t>
+  </si>
+  <si>
+    <t>0.0621,0.0366,0.9344,0.0016</t>
+  </si>
+  <si>
+    <t>0.8079,0.0038,0.1166,0.0291</t>
+  </si>
+  <si>
+    <t>0.1821,0.0047,0.9238,0.0010</t>
+  </si>
+  <si>
+    <t>0.0040,0.9913,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.0065,0.9864,0.0019,0.0023</t>
+  </si>
+  <si>
+    <t>0.0442,0.9359,0.0015,0.0124</t>
+  </si>
+  <si>
+    <t>0.0897,0.9017,0.0150,0.0028</t>
+  </si>
+  <si>
+    <t>0.0356,0.9514,0.0048,0.0056</t>
+  </si>
+  <si>
+    <t>0.0166,0.9705,0.0019,0.0039</t>
+  </si>
+  <si>
+    <t>0.3046,0.7445,0.0171,0.0026</t>
+  </si>
+  <si>
+    <t>0.6098,0.0454,0.3470,0.0499</t>
+  </si>
+  <si>
+    <t>0.4523,0.0124,0.4194,0.1404</t>
+  </si>
+  <si>
+    <t>0.3447,0.3002,0.3317,0.0338</t>
+  </si>
+  <si>
+    <t>0.3903,0.1659,0.4603,0.0387</t>
+  </si>
+  <si>
+    <t>0.0375,0.0192,0.1037,0.9124</t>
+  </si>
+  <si>
+    <t>0.0011,0.9934,0.0162,0.0004</t>
+  </si>
+  <si>
+    <t>0.0034,0.9826,0.0459,0.0010</t>
+  </si>
+  <si>
+    <t>0.0045,0.9501,0.0068,0.4365</t>
+  </si>
+  <si>
+    <t>0.0007,0.9360,0.9274,0.0003</t>
+  </si>
+  <si>
+    <t>0.0087,0.9815,0.0322,0.0003</t>
+  </si>
+  <si>
+    <t>0.5324,0.2977,0.1360,0.0008</t>
+  </si>
+  <si>
+    <t>0.5993,0.4989,0.0162,0.0044</t>
+  </si>
+  <si>
+    <t>0.9774,0.0112,0.0035,0.0024</t>
+  </si>
+  <si>
+    <t>0.9122,0.0706,0.0207,0.0058</t>
+  </si>
+  <si>
+    <t>0.9889,0.0017,0.0007,0.0034</t>
+  </si>
+  <si>
+    <t>0.9394,0.0118,0.0233,0.0079</t>
+  </si>
+  <si>
+    <t>0.9714,0.0133,0.0141,0.0015</t>
+  </si>
+  <si>
+    <t>0.9725,0.0103,0.0073,0.0030</t>
+  </si>
+  <si>
+    <t>0.9599,0.0135,0.0054,0.0078</t>
+  </si>
+  <si>
+    <t>0.9791,0.0078,0.0036,0.0025</t>
+  </si>
+  <si>
+    <t>0.0084,0.5639,0.8629,0.0020</t>
+  </si>
+  <si>
+    <t>0.0100,0.6282,0.8855,0.0033</t>
+  </si>
+  <si>
+    <t>0.0612,0.1180,0.8872,0.0009</t>
+  </si>
+  <si>
+    <t>0.0224,0.4834,0.7737,0.0031</t>
+  </si>
+  <si>
+    <t>0.7695,0.0808,0.1357,0.0277</t>
+  </si>
+  <si>
+    <t>0.7694,0.0114,0.2677,0.0100</t>
+  </si>
+  <si>
+    <t>0.3694,0.0041,0.7255,0.0215</t>
+  </si>
+  <si>
+    <t>0.7406,0.0501,0.1940,0.0370</t>
+  </si>
+  <si>
+    <t>0.0211,0.0032,0.0128,0.9777</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0017,0.9988</t>
+  </si>
+  <si>
+    <t>0.0009,0.0396,0.0015,0.9976</t>
+  </si>
+  <si>
+    <t>0.0105,0.0007,0.0053,0.9907</t>
+  </si>
+  <si>
+    <t>0.0036,0.8759,0.7937,0.0022</t>
+  </si>
+  <si>
+    <t>0.9468,0.0299,0.0141,0.0065</t>
+  </si>
+  <si>
+    <t>0.2135,0.8225,0.0059,0.0190</t>
+  </si>
+  <si>
+    <t>0.9827,0.0010,0.0018,0.0074</t>
+  </si>
+  <si>
+    <t>0.5185,0.5476,0.0162,0.0022</t>
+  </si>
+  <si>
+    <t>0.9367,0.0073,0.0064,0.0293</t>
+  </si>
+  <si>
+    <t>0.1672,0.0034,0.0271,0.8891</t>
+  </si>
+  <si>
+    <t>0.9740,0.0039,0.0057,0.0067</t>
+  </si>
+  <si>
+    <t>0.0173,0.0296,0.9423,0.0392</t>
+  </si>
+  <si>
+    <t>0.7499,0.0027,0.0313,0.1712</t>
+  </si>
+  <si>
+    <t>0.8488,0.0040,0.0058,0.1166</t>
+  </si>
+  <si>
+    <t>0.3980,0.5496,0.1193,0.0171</t>
+  </si>
+  <si>
+    <t>0.8695,0.0830,0.0316,0.0040</t>
+  </si>
+  <si>
+    <t>0.8866,0.0400,0.0684,0.0037</t>
+  </si>
+  <si>
+    <t>0.4569,0.3712,0.0607,0.0542</t>
+  </si>
+  <si>
+    <t>0.7888,0.0862,0.1280,0.0042</t>
+  </si>
+  <si>
+    <t>0.7551,0.2132,0.0499,0.0048</t>
+  </si>
+  <si>
+    <t>0.9734,0.0041,0.0058,0.0076</t>
+  </si>
+  <si>
+    <t>0.9780,0.0134,0.0047,0.0016</t>
+  </si>
+  <si>
+    <t>0.9900,0.0022,0.0017,0.0014</t>
+  </si>
+  <si>
+    <t>0.9834,0.0013,0.0036,0.0041</t>
+  </si>
+  <si>
+    <t>0.9730,0.0046,0.0102,0.0043</t>
+  </si>
+  <si>
+    <t>0.9791,0.0105,0.0057,0.0013</t>
+  </si>
+  <si>
+    <t>0.9859,0.0037,0.0028,0.0023</t>
+  </si>
+  <si>
+    <t>0.9824,0.0058,0.0066,0.0012</t>
+  </si>
+  <si>
+    <t>0.5660,0.5415,0.0033,0.0037</t>
+  </si>
+  <si>
+    <t>0.5127,0.5829,0.0136,0.0017</t>
+  </si>
+  <si>
+    <t>0.4314,0.6666,0.0092,0.0046</t>
+  </si>
+  <si>
+    <t>0.7170,0.1702,0.1664,0.0225</t>
+  </si>
+  <si>
+    <t>0.9449,0.0618,0.0037,0.0009</t>
+  </si>
+  <si>
+    <t>0.6227,0.3625,0.0812,0.0185</t>
+  </si>
+  <si>
+    <t>0.9473,0.0547,0.0061,0.0009</t>
+  </si>
+  <si>
+    <t>0.8210,0.2034,0.0180,0.0037</t>
+  </si>
+  <si>
+    <t>0.0055,0.0557,0.9886,0.0013</t>
+  </si>
+  <si>
+    <t>0.8875,0.0957,0.0281,0.0032</t>
+  </si>
+  <si>
+    <t>0.0010,0.0025,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.0458,0.9920,0.0008</t>
+  </si>
+  <si>
+    <t>0.0084,0.0030,0.9887,0.0030</t>
+  </si>
+  <si>
+    <t>0.0157,0.0502,0.9711,0.0019</t>
+  </si>
+  <si>
+    <t>0.0338,0.0025,0.9834,0.0003</t>
+  </si>
+  <si>
+    <t>0.0216,0.0014,0.9833,0.0015</t>
+  </si>
+  <si>
+    <t>0.0275,0.0202,0.9689,0.0006</t>
+  </si>
+  <si>
+    <t>0.2082,0.0120,0.8499,0.0097</t>
+  </si>
+  <si>
+    <t>0.2356,0.0139,0.8490,0.0033</t>
+  </si>
+  <si>
+    <t>0.6784,0.1032,0.2602,0.0089</t>
+  </si>
+  <si>
+    <t>0.3458,0.2352,0.3770,0.0041</t>
+  </si>
+  <si>
+    <t>0.2213,0.5108,0.1491,0.0005</t>
+  </si>
+  <si>
+    <t>0.6375,0.0462,0.3682,0.0010</t>
+  </si>
+  <si>
+    <t>0.5550,0.1140,0.3964,0.0351</t>
+  </si>
+  <si>
+    <t>0.2393,0.0450,0.7618,0.0094</t>
+  </si>
+  <si>
+    <t>0.8806,0.1417,0.0127,0.0031</t>
+  </si>
+  <si>
+    <t>0.0762,0.9172,0.0023,0.0065</t>
+  </si>
+  <si>
+    <t>0.8166,0.1798,0.0407,0.0077</t>
+  </si>
+  <si>
+    <t>0.9292,0.0640,0.0112,0.0056</t>
+  </si>
+  <si>
+    <t>0.7278,0.3150,0.0161,0.0084</t>
+  </si>
+  <si>
+    <t>0.6595,0.0559,0.3113,0.0017</t>
+  </si>
+  <si>
+    <t>0.6814,0.0123,0.4744,0.0077</t>
+  </si>
+  <si>
+    <t>0.6304,0.0742,0.2235,0.0534</t>
+  </si>
+  <si>
+    <t>0.3210,0.0021,0.7892,0.0092</t>
+  </si>
+  <si>
+    <t>0.8911,0.0045,0.0242,0.0319</t>
+  </si>
+  <si>
+    <t>0.7094,0.0266,0.2624,0.0441</t>
+  </si>
+  <si>
+    <t>0.0698,0.4884,0.6983,0.0332</t>
+  </si>
+  <si>
+    <t>0.0621,0.0300,0.9392,0.0175</t>
+  </si>
+  <si>
+    <t>0.0468,0.0314,0.9401,0.0039</t>
+  </si>
+  <si>
+    <t>0.0332,0.3099,0.8355,0.0073</t>
+  </si>
+  <si>
+    <t>0.9860,0.0049,0.0011,0.0022</t>
+  </si>
+  <si>
+    <t>0.9873,0.0070,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.9757,0.0099,0.0025,0.0034</t>
+  </si>
+  <si>
+    <t>0.9576,0.0436,0.0053,0.0013</t>
+  </si>
+  <si>
+    <t>0.9560,0.0315,0.0100,0.0033</t>
+  </si>
+  <si>
+    <t>0.9880,0.0062,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9554,0.0179,0.0013,0.0091</t>
+  </si>
+  <si>
+    <t>0.9490,0.0199,0.0036,0.0086</t>
+  </si>
+  <si>
+    <t>0.0390,0.0200,0.9727,0.0008</t>
+  </si>
+  <si>
+    <t>0.2491,0.0898,0.7538,0.0055</t>
+  </si>
+  <si>
+    <t>0.7360,0.0479,0.0941,0.1254</t>
+  </si>
+  <si>
+    <t>0.0018,0.0051,0.9925,0.0051</t>
+  </si>
+  <si>
+    <t>0.0018,0.0044,0.9922,0.0081</t>
+  </si>
+  <si>
+    <t>0.0894,0.0626,0.9017,0.0034</t>
+  </si>
+  <si>
+    <t>0.0010,0.0030,0.9962,0.0027</t>
+  </si>
+  <si>
+    <t>0.0146,0.1165,0.9293,0.0007</t>
+  </si>
+  <si>
+    <t>0.0017,0.0104,0.9947,0.0019</t>
+  </si>
+  <si>
+    <t>0.0018,0.0071,0.9883,0.0104</t>
+  </si>
+  <si>
+    <t>0.0931,0.0218,0.9166,0.0074</t>
+  </si>
+  <si>
+    <t>0.7151,0.0063,0.4642,0.0039</t>
+  </si>
+  <si>
+    <t>0.5886,0.0048,0.2946,0.0746</t>
+  </si>
+  <si>
+    <t>0.8120,0.0077,0.2041,0.0127</t>
+  </si>
+  <si>
+    <t>0.9761,0.0214,0.0013,0.0017</t>
+  </si>
+  <si>
+    <t>0.9927,0.0028,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9879,0.0073,0.0028,0.0004</t>
+  </si>
+  <si>
+    <t>0.9755,0.0157,0.0054,0.0013</t>
+  </si>
+  <si>
+    <t>0.9798,0.0069,0.0050,0.0023</t>
+  </si>
+  <si>
+    <t>0.9403,0.0489,0.0098,0.0022</t>
+  </si>
+  <si>
+    <t>0.9713,0.0150,0.0051,0.0033</t>
+  </si>
+  <si>
+    <t>0.9812,0.0045,0.0043,0.0042</t>
+  </si>
+  <si>
+    <t>0.0115,0.5005,0.7260,0.0007</t>
+  </si>
+  <si>
+    <t>0.0121,0.0782,0.9750,0.0022</t>
+  </si>
+  <si>
+    <t>0.0169,0.1408,0.9518,0.0034</t>
+  </si>
+  <si>
+    <t>0.1202,0.0871,0.8085,0.0103</t>
+  </si>
+  <si>
+    <t>0.0384,0.0458,0.9503,0.0042</t>
+  </si>
+  <si>
+    <t>0.4065,0.0080,0.3673,0.1776</t>
+  </si>
+  <si>
+    <t>0.1190,0.0723,0.7934,0.0422</t>
+  </si>
+  <si>
+    <t>0.0020,0.0080,0.9312,0.1475</t>
+  </si>
+  <si>
+    <t>0.7494,0.0023,0.0210,0.2511</t>
+  </si>
+  <si>
+    <t>0.0132,0.0117,0.0020,0.9919</t>
+  </si>
+  <si>
+    <t>0.0583,0.0017,0.0018,0.9782</t>
+  </si>
+  <si>
+    <t>0.0041,0.0009,0.0011,0.9968</t>
+  </si>
+  <si>
+    <t>0.0144,0.0004,0.0002,0.9955</t>
+  </si>
+  <si>
+    <t>0.0805,0.0295,0.0160,0.9510</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2147,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,10 +2637,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2651,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3575,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,10 +4849,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,10 +5339,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
